--- a/temp_excel_files/Sanlam.xlsx
+++ b/temp_excel_files/Sanlam.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29311"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://citybrokersltdmu.sharepoint.com/sites/Accounts/Shared Documents/INSURERS/STATEMENTS &amp; RECONS/2024-2025/Reconciliation 30.06.2025/FRCI/Sanlam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{554FBEDD-B61C-4C5F-A082-A08C29DE64DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{554FBEDD-B61C-4C5F-A082-A08C29DE64DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{975DDCED-A59E-4889-B50C-0F8037487217}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA6C7F24-1F0D-4D39-BA87-3BD657B3FCF6}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Final!$A$1:$K$51</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -451,10 +451,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="d/mm/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="d/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -594,37 +594,37 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -967,22 +967,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="86.109375" customWidth="1"/>
+    <col min="1" max="1" width="34.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="86.140625" customWidth="1"/>
     <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="28.9">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -997,7 +997,7 @@
       <c r="J1" s="18"/>
       <c r="K1" s="18"/>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="28.9">
       <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
@@ -1012,7 +1012,7 @@
       <c r="J2" s="18"/>
       <c r="K2" s="18"/>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:11" s="1" customFormat="1" ht="28.9">
       <c r="A3" s="18" t="s">
         <v>2</v>
       </c>
@@ -1027,7 +1027,7 @@
       <c r="J3" s="18"/>
       <c r="K3" s="18"/>
     </row>
-    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="15" thickBot="1">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="11" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" s="11" customFormat="1" ht="15" thickBot="1">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11">
       <c r="A6" s="12" t="s">
         <v>13</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>683315.7</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11">
       <c r="A7" s="12" t="s">
         <v>17</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>442554</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11">
       <c r="A8" s="12" t="s">
         <v>21</v>
       </c>
@@ -1161,7 +1161,7 @@
       <c r="J8" s="15"/>
       <c r="K8" s="14"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11">
       <c r="A9" s="12" t="s">
         <v>24</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>281316.26</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11">
       <c r="A10" s="12" t="s">
         <v>28</v>
       </c>
@@ -1219,7 +1219,7 @@
       <c r="J10" s="15"/>
       <c r="K10" s="14"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11">
       <c r="A11" s="12" t="s">
         <v>30</v>
       </c>
@@ -1251,7 +1251,7 @@
         <v>417548.44</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11">
       <c r="A12" s="12" t="s">
         <v>34</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>86750.34</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11">
       <c r="A13" s="12" t="s">
         <v>38</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>259851.19</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11">
       <c r="A14" s="12" t="s">
         <v>42</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>4868.7</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11">
       <c r="A15" s="12"/>
       <c r="B15" s="13"/>
       <c r="C15" s="12"/>
@@ -1365,7 +1365,7 @@
         <v>23287.94</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11">
       <c r="A16" s="12" t="s">
         <v>46</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>604899.41</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11">
       <c r="A17" s="12" t="s">
         <v>50</v>
       </c>
@@ -1423,7 +1423,7 @@
       <c r="J17" s="15"/>
       <c r="K17" s="14"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11">
       <c r="A18" s="12" t="s">
         <v>53</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>570911.38</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11">
       <c r="A19" s="12" t="s">
         <v>57</v>
       </c>
@@ -1481,7 +1481,7 @@
       <c r="J19" s="15"/>
       <c r="K19" s="14"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11">
       <c r="A20" s="12" t="s">
         <v>60</v>
       </c>
@@ -1507,7 +1507,7 @@
       <c r="J20" s="15"/>
       <c r="K20" s="14"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11">
       <c r="A21" s="12" t="s">
         <v>61</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>28721.32</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11">
       <c r="A22" s="12"/>
       <c r="B22" s="13"/>
       <c r="C22" s="12"/>
@@ -1557,7 +1557,7 @@
         <v>131148.74</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11">
       <c r="A23" s="12" t="s">
         <v>66</v>
       </c>
@@ -1583,7 +1583,7 @@
       <c r="J23" s="15"/>
       <c r="K23" s="14"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11">
       <c r="A24" s="12" t="s">
         <v>68</v>
       </c>
@@ -1609,7 +1609,7 @@
       <c r="J24" s="15"/>
       <c r="K24" s="14"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11">
       <c r="A25" s="12" t="s">
         <v>69</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>4537.1000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11">
       <c r="A26" s="12" t="s">
         <v>73</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>717168.47</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11">
       <c r="A27" s="12" t="s">
         <v>77</v>
       </c>
@@ -1699,7 +1699,7 @@
       <c r="J27" s="15"/>
       <c r="K27" s="14"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11">
       <c r="A28" s="12" t="s">
         <v>79</v>
       </c>
@@ -1725,7 +1725,7 @@
       <c r="J28" s="15"/>
       <c r="K28" s="14"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11">
       <c r="A29" s="12" t="s">
         <v>82</v>
       </c>
@@ -1751,7 +1751,7 @@
       <c r="J29" s="15"/>
       <c r="K29" s="14"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11">
       <c r="A30" s="12" t="s">
         <v>85</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>71904.820000000007</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11">
       <c r="A31" s="12" t="s">
         <v>89</v>
       </c>
@@ -1809,7 +1809,7 @@
       <c r="J31" s="15"/>
       <c r="K31" s="14"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11">
       <c r="A32" s="12" t="s">
         <v>92</v>
       </c>
@@ -1835,7 +1835,7 @@
       <c r="J32" s="15"/>
       <c r="K32" s="14"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11">
       <c r="A33" s="12" t="s">
         <v>95</v>
       </c>
@@ -1861,7 +1861,7 @@
       <c r="J33" s="15"/>
       <c r="K33" s="14"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11">
       <c r="A34" s="12" t="s">
         <v>98</v>
       </c>
@@ -1887,7 +1887,7 @@
       <c r="J34" s="15"/>
       <c r="K34" s="14"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11">
       <c r="A35" s="12" t="s">
         <v>99</v>
       </c>
@@ -1913,7 +1913,7 @@
       <c r="J35" s="15"/>
       <c r="K35" s="14"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11">
       <c r="A36" s="12" t="s">
         <v>101</v>
       </c>
@@ -1939,7 +1939,7 @@
       <c r="J36" s="15"/>
       <c r="K36" s="14"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11">
       <c r="A37" s="12" t="s">
         <v>103</v>
       </c>
@@ -1965,7 +1965,7 @@
       <c r="J37" s="15"/>
       <c r="K37" s="14"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11">
       <c r="A38" s="12" t="s">
         <v>105</v>
       </c>
@@ -1991,7 +1991,7 @@
       <c r="J38" s="15"/>
       <c r="K38" s="14"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11">
       <c r="A39" s="12" t="s">
         <v>107</v>
       </c>
@@ -2017,7 +2017,7 @@
       <c r="J39" s="15"/>
       <c r="K39" s="14"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11">
       <c r="A40" s="12" t="s">
         <v>108</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>94602.37</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11">
       <c r="A41" s="12" t="s">
         <v>112</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>93360.61</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11">
       <c r="A42" s="12" t="s">
         <v>114</v>
       </c>
@@ -2107,7 +2107,7 @@
       <c r="J42" s="15"/>
       <c r="K42" s="14"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11">
       <c r="A43" s="12" t="s">
         <v>116</v>
       </c>
@@ -2139,7 +2139,7 @@
         <v>88986.37</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11">
       <c r="A44" s="12" t="s">
         <v>119</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>524906</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11">
       <c r="A45" s="12" t="s">
         <v>123</v>
       </c>
@@ -2197,7 +2197,7 @@
       <c r="J45" s="15"/>
       <c r="K45" s="14"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11">
       <c r="A46" s="12" t="s">
         <v>126</v>
       </c>
@@ -2223,7 +2223,7 @@
       <c r="J46" s="15"/>
       <c r="K46" s="14"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11">
       <c r="A47" s="12" t="s">
         <v>129</v>
       </c>
@@ -2249,7 +2249,7 @@
       <c r="J47" s="15"/>
       <c r="K47" s="14"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11">
       <c r="A48" s="12" t="s">
         <v>131</v>
       </c>
@@ -2275,7 +2275,7 @@
       <c r="J48" s="15"/>
       <c r="K48" s="14"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11">
       <c r="A49" s="12" t="s">
         <v>133</v>
       </c>
@@ -2301,7 +2301,7 @@
       <c r="J49" s="15"/>
       <c r="K49" s="14"/>
     </row>
-    <row r="50" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" ht="15" thickBot="1">
       <c r="E50" s="17">
         <f>SUM(E6:E49)</f>
         <v>17445525.009999998</v>
@@ -2319,7 +2319,7 @@
         <v>5130639.1600000011</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="1:11" ht="15" thickTop="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:K1"/>
@@ -2335,20 +2335,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Status xmlns="411d9a0c-6800-433f-905c-961176f6889b">In Progress</Status>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Status xmlns="411d9a0c-6800-433f-905c-961176f6889b">In Progress</Status>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2502,22 +2502,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57714765-0D08-49AC-9FFD-1759A253888E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ad474b94-ba02-4e88-987e-f92536b7745b"/>
-    <ds:schemaRef ds:uri="5aff64d6-7803-4fb3-a6dc-2c7b0357e73e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9F5D2C1-41F1-4BE8-8D1C-DA9CB3ABE51B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9F5D2C1-41F1-4BE8-8D1C-DA9CB3ABE51B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57714765-0D08-49AC-9FFD-1759A253888E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
